--- a/eval/results/evaluation_metrics_fisher_new30.xlsx
+++ b/eval/results/evaluation_metrics_fisher_new30.xlsx
@@ -431,202 +431,202 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>samples</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p_acc_fisher</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>adj_p_acc_fisher</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>p_prec_fisher</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>adj_p_prec_fisher</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>p_rec_fisher</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>adj_p_rec_fisher</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tp</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tn</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>fp</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>fn</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_p_accuracy</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_adj_p_accuracy</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_p_precision</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_adj_p_precision</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_p_recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_adj_p_recall</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>fisher_p_f1</t>
+          <t>p_f1_fisher</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>fisher_adj_p_f1</t>
+          <t>adj_p_f1_fisher</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>480</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GPT-4o base</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>227</v>
+      </c>
+      <c r="E2" t="n">
+        <v>168</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.8229166666666666</v>
       </c>
-      <c r="C2" t="n">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>0.8438661710037175</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.8407407407407408</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.842300556586271</v>
-      </c>
-      <c r="F2" t="n">
-        <v>227</v>
-      </c>
-      <c r="G2" t="n">
-        <v>168</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42</v>
-      </c>
-      <c r="I2" t="n">
-        <v>43</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>GPT-4o base</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>0.8407407407407408</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0.842300556586271</v>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>480</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>227</v>
+      </c>
+      <c r="E3" t="n">
+        <v>184</v>
+      </c>
+      <c r="F3" t="n">
+        <v>26</v>
+      </c>
+      <c r="G3" t="n">
+        <v>43</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.85625</v>
       </c>
-      <c r="C3" t="n">
+      <c r="I3" t="n">
+        <v>0.1869901749974171</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2804852624961257</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.8972332015810277</v>
       </c>
-      <c r="D3" t="n">
+      <c r="L3" t="n">
+        <v>0.09025478031425586</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2707643409427676</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.8407407407407408</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.8680688336520077</v>
-      </c>
-      <c r="F3" t="n">
-        <v>227</v>
-      </c>
-      <c r="G3" t="n">
-        <v>184</v>
-      </c>
-      <c r="H3" t="n">
-        <v>26</v>
-      </c>
-      <c r="I3" t="n">
-        <v>43</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GPT-4o FT</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.1869901749974171</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.2804852624961257</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.09025478031425586</v>
-      </c>
       <c r="O3" t="n">
-        <v>0.2707643409427676</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.8680688336520077</v>
       </c>
       <c r="R3" t="n">
         <v>0.257330901601268</v>
@@ -636,60 +636,60 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>480</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPT-4o QSP</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198</v>
+      </c>
+      <c r="E4" t="n">
+        <v>178</v>
+      </c>
+      <c r="F4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.7833333333333333</v>
       </c>
-      <c r="C4" t="n">
+      <c r="I4" t="n">
+        <v>0.1438850492239398</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2804852624961257</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.8608695652173913</v>
       </c>
-      <c r="D4" t="n">
+      <c r="L4" t="n">
+        <v>0.6154557141356378</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.7385468569627653</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="E4" t="n">
+      <c r="O4" t="n">
+        <v>0.003140124997037771</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.006280249994075541</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.7919999999999999</v>
-      </c>
-      <c r="F4" t="n">
-        <v>198</v>
-      </c>
-      <c r="G4" t="n">
-        <v>178</v>
-      </c>
-      <c r="H4" t="n">
-        <v>32</v>
-      </c>
-      <c r="I4" t="n">
-        <v>72</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>GPT-4o QSP</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1438850492239398</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.2804852624961257</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.6154557141356378</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.7385468569627653</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.003140124997037771</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.006280249994075541</v>
       </c>
       <c r="R4" t="n">
         <v>0.03672237564728741</v>
@@ -699,107 +699,107 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>480</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B base</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>223</v>
+      </c>
+      <c r="E5" t="n">
+        <v>168</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G5" t="n">
+        <v>47</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.8145833333333333</v>
       </c>
-      <c r="C5" t="n">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>0.8415094339622642</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.825925925925926</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.8336448598130841</v>
-      </c>
-      <c r="F5" t="n">
-        <v>223</v>
-      </c>
-      <c r="G5" t="n">
-        <v>168</v>
-      </c>
-      <c r="H5" t="n">
-        <v>42</v>
-      </c>
-      <c r="I5" t="n">
-        <v>47</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B base</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0.825925925925926</v>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>0.8336448598130841</v>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>480</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>186</v>
+      </c>
+      <c r="E6" t="n">
+        <v>184</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>84</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="C6" t="n">
+      <c r="I6" t="n">
+        <v>0.111152644265034</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2804852624961257</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.8773584905660378</v>
       </c>
-      <c r="D6" t="n">
+      <c r="L6" t="n">
+        <v>0.2932601979885175</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5865203959770351</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.6888888888888889</v>
       </c>
-      <c r="E6" t="n">
+      <c r="O6" t="n">
+        <v>0.0002823324270744563</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.000846997281223369</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.7717842323651452</v>
-      </c>
-      <c r="F6" t="n">
-        <v>186</v>
-      </c>
-      <c r="G6" t="n">
-        <v>184</v>
-      </c>
-      <c r="H6" t="n">
-        <v>26</v>
-      </c>
-      <c r="I6" t="n">
-        <v>84</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B FT</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.111152644265034</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.2804852624961257</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.2932601979885175</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.5865203959770351</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.0002823324270744563</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.000846997281223369</v>
       </c>
       <c r="R6" t="n">
         <v>0.01414015346878846</v>
@@ -809,60 +809,60 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>480</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B QSP</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>214</v>
+      </c>
+      <c r="E7" t="n">
+        <v>188</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>56</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.8375</v>
       </c>
-      <c r="C7" t="n">
+      <c r="I7" t="n">
+        <v>0.3945859354881172</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4735031225857406</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.9067796610169492</v>
       </c>
-      <c r="D7" t="n">
+      <c r="L7" t="n">
+        <v>0.03204639247025044</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1922783548215027</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.7925925925925926</v>
       </c>
-      <c r="E7" t="n">
+      <c r="O7" t="n">
+        <v>0.3809588080729812</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4571505696875775</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.8458498023715416</v>
-      </c>
-      <c r="F7" t="n">
-        <v>214</v>
-      </c>
-      <c r="G7" t="n">
-        <v>188</v>
-      </c>
-      <c r="H7" t="n">
-        <v>22</v>
-      </c>
-      <c r="I7" t="n">
-        <v>56</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B QSP</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3945859354881172</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.4735031225857406</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.03204639247025044</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.1922783548215027</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.3809588080729812</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.4571505696875775</v>
       </c>
       <c r="R7" t="n">
         <v>0.6128797461344258</v>
@@ -872,107 +872,107 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>480</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B base</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>166</v>
+      </c>
+      <c r="E8" t="n">
+        <v>170</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" t="n">
+        <v>104</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>0.8058252427184466</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.6148148148148148</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.6974789915966386</v>
-      </c>
-      <c r="F8" t="n">
-        <v>166</v>
-      </c>
-      <c r="G8" t="n">
-        <v>170</v>
-      </c>
-      <c r="H8" t="n">
-        <v>40</v>
-      </c>
-      <c r="I8" t="n">
-        <v>104</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B base</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0.6148148148148148</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>0.6974789915966386</v>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>480</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>143</v>
+      </c>
+      <c r="E9" t="n">
+        <v>182</v>
+      </c>
+      <c r="F9" t="n">
+        <v>28</v>
+      </c>
+      <c r="G9" t="n">
+        <v>127</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="C9" t="n">
+      <c r="I9" t="n">
+        <v>0.4858693309816747</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4858693309816747</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.8362573099415205</v>
       </c>
-      <c r="D9" t="n">
+      <c r="L9" t="n">
+        <v>0.501879867678392</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.7385468569627653</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.5296296296296297</v>
       </c>
-      <c r="E9" t="n">
+      <c r="O9" t="n">
+        <v>0.0555719925755639</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.08335798886334586</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0.6485260770975058</v>
-      </c>
-      <c r="F9" t="n">
-        <v>143</v>
-      </c>
-      <c r="G9" t="n">
-        <v>182</v>
-      </c>
-      <c r="H9" t="n">
-        <v>28</v>
-      </c>
-      <c r="I9" t="n">
-        <v>127</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B FT</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.4858693309816747</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.4858693309816747</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.501879867678392</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.7385468569627653</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.0555719925755639</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.08335798886334586</v>
       </c>
       <c r="R9" t="n">
         <v>0.1211595077987267</v>
@@ -982,60 +982,60 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>480</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>208</v>
+      </c>
+      <c r="E10" t="n">
+        <v>161</v>
+      </c>
+      <c r="F10" t="n">
+        <v>49</v>
+      </c>
+      <c r="G10" t="n">
+        <v>62</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.76875</v>
       </c>
-      <c r="C10" t="n">
+      <c r="I10" t="n">
+        <v>0.01926579067113064</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1155947440267838</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.8093385214007782</v>
       </c>
-      <c r="D10" t="n">
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.7703703703703704</v>
       </c>
-      <c r="E10" t="n">
+      <c r="O10" t="n">
+        <v>0.0001241991287845277</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.000745194772707166</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.7893738140417458</v>
-      </c>
-      <c r="F10" t="n">
-        <v>208</v>
-      </c>
-      <c r="G10" t="n">
-        <v>161</v>
-      </c>
-      <c r="H10" t="n">
-        <v>49</v>
-      </c>
-      <c r="I10" t="n">
-        <v>62</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B QSP</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.01926579067113064</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.1155947440267838</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.0001241991287845277</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.000745194772707166</v>
       </c>
       <c r="R10" t="n">
         <v>0.001062599416653957</v>

--- a/eval/results/evaluation_metrics_fisher_new30.xlsx
+++ b/eval/results/evaluation_metrics_fisher_new30.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="E2" t="n">
         <v>168</v>
@@ -549,25 +549,25 @@
         <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0.8438661710037175</v>
+        <v>0.832</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0.8407407407407408</v>
+        <v>0.7703703703703704</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0.842300556586271</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E3" t="n">
         <v>184</v>
@@ -596,43 +596,43 @@
         <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="H3" t="n">
-        <v>0.85625</v>
+        <v>0.8125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1869901749974171</v>
+        <v>0.2960704006348283</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2804852624961257</v>
+        <v>0.5919051066731024</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8972332015810277</v>
+        <v>0.8879310344827587</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09025478031425586</v>
+        <v>0.08896587626377728</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2707643409427676</v>
+        <v>0.2668976287913318</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8407407407407408</v>
+        <v>0.762962962962963</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.9189918677222855</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0.9189918677222856</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8680688336520077</v>
+        <v>0.8207171314741036</v>
       </c>
       <c r="R3" t="n">
-        <v>0.257330901601268</v>
+        <v>0.4253205778159825</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3087970819215217</v>
+        <v>0.510384693379179</v>
       </c>
     </row>
     <row r="4">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E4" t="n">
         <v>178</v>
@@ -659,43 +659,43 @@
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7833333333333333</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1438850492239398</v>
+        <v>0.6982752643584706</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2804852624961257</v>
+        <v>0.6982752643584705</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8608695652173913</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6154557141356378</v>
+        <v>0.5265252658102896</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7385468569627653</v>
+        <v>0.6318303189723474</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003140124997037771</v>
+        <v>0.1406020980811203</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006280249994075541</v>
+        <v>0.2109031471216804</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7919999999999999</v>
+        <v>0.777327935222672</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03672237564728741</v>
+        <v>0.3974682749882148</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07344475129457481</v>
+        <v>0.510384693379179</v>
       </c>
     </row>
     <row r="5">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E5" t="n">
         <v>168</v>
@@ -722,25 +722,25 @@
         <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8145833333333333</v>
+        <v>0.7958333333333333</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.8415094339622642</v>
+        <v>0.8359375</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.825925925925926</v>
+        <v>0.7925925925925926</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0.8336448598130841</v>
+        <v>0.8136882129277566</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E6" t="n">
         <v>184</v>
@@ -769,43 +769,43 @@
         <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.111152644265034</v>
+        <v>0.2431292311903027</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2804852624961257</v>
+        <v>0.5919051066731024</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8773584905660378</v>
+        <v>0.875</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2932601979885175</v>
+        <v>0.2910282341557326</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5865203959770351</v>
+        <v>0.5820564683114652</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.674074074074074</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002823324270744563</v>
+        <v>0.002488175020327776</v>
       </c>
       <c r="P6" t="n">
-        <v>0.000846997281223369</v>
+        <v>0.007464525060983327</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7717842323651452</v>
+        <v>0.7615062761506276</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01414015346878846</v>
+        <v>0.04445649231862993</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04242046040636538</v>
+        <v>0.1333694769558898</v>
       </c>
     </row>
     <row r="7">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="E7" t="n">
         <v>188</v>
@@ -832,43 +832,43 @@
         <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8375</v>
+        <v>0.81875</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3945859354881172</v>
+        <v>0.4132479807430159</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4735031225857406</v>
+        <v>0.5919051066731024</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9067796610169492</v>
+        <v>0.9030837004405287</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03204639247025044</v>
+        <v>0.03188127775127045</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1922783548215027</v>
+        <v>0.1912876665076227</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7925925925925926</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3809588080729812</v>
+        <v>0.4090788921345193</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4571505696875775</v>
+        <v>0.4908946705614231</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8458498023715416</v>
+        <v>0.8249496981891349</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6128797461344258</v>
+        <v>0.6846473339860362</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6128797461344258</v>
+        <v>0.6846473339860362</v>
       </c>
     </row>
     <row r="8">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E8" t="n">
         <v>170</v>
@@ -895,25 +895,25 @@
         <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7</v>
+        <v>0.6791666666666667</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.8058252427184466</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.6148148148148148</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>0.6974789915966386</v>
+        <v>0.6695278969957081</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E9" t="n">
         <v>182</v>
@@ -942,43 +942,43 @@
         <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4858693309816747</v>
+        <v>0.4932542555609186</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4858693309816747</v>
+        <v>0.5919051066731024</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8362573099415205</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="L9" t="n">
-        <v>0.501879867678392</v>
+        <v>0.5005093836949801</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7385468569627653</v>
+        <v>0.6318303189723474</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5296296296296297</v>
+        <v>0.4925925925925926</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0555719925755639</v>
+        <v>0.05757237282240871</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08335798886334586</v>
+        <v>0.1151447456448174</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6485260770975058</v>
+        <v>0.617169373549884</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1211595077987267</v>
+        <v>0.1085866083759338</v>
       </c>
       <c r="S9" t="n">
-        <v>0.18173926169809</v>
+        <v>0.2171732167518675</v>
       </c>
     </row>
     <row r="10">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E10" t="n">
         <v>161</v>
@@ -1005,43 +1005,43 @@
         <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H10" t="n">
-        <v>0.76875</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01926579067113064</v>
+        <v>0.01210550487892716</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1155947440267838</v>
+        <v>0.07263302927356295</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8093385214007782</v>
+        <v>0.804</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.9050652620974227</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.9050652620974228</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7703703703703704</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0001241991287845277</v>
+        <v>5.967567535965387e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.000745194772707166</v>
+        <v>0.0003580540521579232</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7893738140417458</v>
+        <v>0.7730769230769231</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001062599416653957</v>
+        <v>0.0003503069803788874</v>
       </c>
       <c r="S10" t="n">
-        <v>0.006375596499923739</v>
+        <v>0.002101841882273325</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_new30.xlsx
+++ b/eval/results/evaluation_metrics_fisher_new30.xlsx
@@ -590,7 +590,7 @@
         <v>0.2279052731473465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3603777460301888</v>
+        <v>0.3894321874804655</v>
       </c>
       <c r="J3" t="n">
         <v>0.8884120171673819</v>
@@ -599,7 +599,7 @@
         <v>0.08839342621879118</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1591081671938241</v>
+        <v>0.1988852089922802</v>
       </c>
       <c r="M3" t="n">
         <v>0.7666666666666667</v>
@@ -648,7 +648,7 @@
         <v>0.02602346303778495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07807038911335484</v>
+        <v>0.1171055836700323</v>
       </c>
       <c r="J4" t="n">
         <v>0.9177489177489178</v>
@@ -657,7 +657,7 @@
         <v>0.005769855204427897</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02596434841992554</v>
+        <v>0.05192869683985107</v>
       </c>
       <c r="M4" t="n">
         <v>0.7851851851851852</v>
@@ -675,7 +675,7 @@
         <v>0.04947522530346203</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1113192569327896</v>
+        <v>0.1484256759103861</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +724,7 @@
         <v>0.322683123188597</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5808296217394746</v>
+        <v>0.7260370271743433</v>
       </c>
       <c r="P5" t="n">
         <v>0.7871485943775101</v>
@@ -806,7 +806,7 @@
         <v>0.1843526344432495</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3603777460301888</v>
+        <v>0.3894321874804655</v>
       </c>
       <c r="J7" t="n">
         <v>0.875</v>
@@ -815,7 +815,7 @@
         <v>0.2914771511575119</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4372157267362679</v>
+        <v>0.5058723775351076</v>
       </c>
       <c r="M7" t="n">
         <v>0.674074074074074</v>
@@ -824,7 +824,7 @@
         <v>0.001212149850067795</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003636449550203385</v>
+        <v>0.005454674325305077</v>
       </c>
       <c r="P7" t="n">
         <v>0.7615062761506276</v>
@@ -833,7 +833,7 @@
         <v>0.02965208763324016</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08895626289972049</v>
+        <v>0.1334343943495807</v>
       </c>
     </row>
     <row r="8">
@@ -864,7 +864,7 @@
         <v>0.2802938024679246</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3603777460301888</v>
+        <v>0.3894321874804655</v>
       </c>
       <c r="J8" t="n">
         <v>0.9051724137931034</v>
@@ -873,7 +873,7 @@
         <v>0.03131207263621193</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07045216343147684</v>
+        <v>0.09393621790863578</v>
       </c>
       <c r="M8" t="n">
         <v>0.7777777777777778</v>
@@ -922,7 +922,7 @@
         <v>0.2802938024679246</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3603777460301888</v>
+        <v>0.3894321874804655</v>
       </c>
       <c r="J9" t="n">
         <v>0.9051724137931034</v>
@@ -931,7 +931,7 @@
         <v>0.03131207263621193</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07045216343147684</v>
+        <v>0.09393621790863578</v>
       </c>
       <c r="M9" t="n">
         <v>0.7777777777777778</v>
@@ -1040,7 +1040,7 @@
         <v>0.04662325538338093</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1049023246126071</v>
+        <v>0.1398697661501428</v>
       </c>
       <c r="P11" t="n">
         <v>0.6267281105990783</v>
@@ -1049,7 +1049,7 @@
         <v>0.09307357223718898</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1675324300269402</v>
+        <v>0.2094155375336752</v>
       </c>
     </row>
     <row r="12">
@@ -1062,52 +1062,52 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="E12" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3875</v>
+        <v>0.6541666666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>1.071521693237782e-20</v>
+        <v>0.3028917013736954</v>
       </c>
       <c r="I12" t="n">
-        <v>9.643695239140039e-20</v>
+        <v>0.3894321874804655</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.7574257425742574</v>
       </c>
       <c r="K12" t="n">
-        <v>5.63631232879145e-13</v>
+        <v>0.3372482516900718</v>
       </c>
       <c r="L12" t="n">
-        <v>5.072681095912305e-12</v>
+        <v>0.5058723775351076</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="N12" t="n">
-        <v>1.099007611182292e-22</v>
+        <v>0.6009687544612505</v>
       </c>
       <c r="O12" t="n">
-        <v>9.891068500640624e-22</v>
+        <v>0.7648309444386462</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2538071065989848</v>
+        <v>0.6483050847457626</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.341111898020201e-37</v>
+        <v>0.3011314171654854</v>
       </c>
       <c r="R12" t="n">
-        <v>5.70700070821818e-36</v>
+        <v>0.5076543255418704</v>
       </c>
     </row>
     <row r="13">
@@ -1138,7 +1138,7 @@
         <v>0.01133281140353123</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05099765131589053</v>
+        <v>0.1019953026317811</v>
       </c>
       <c r="J13" t="n">
         <v>0.8070866141732284</v>
@@ -1156,7 +1156,7 @@
         <v>4.88734866985438e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0002199306901434471</v>
+        <v>0.0004398613802868943</v>
       </c>
       <c r="P13" t="n">
         <v>0.7824427480916031</v>
@@ -1165,7 +1165,7 @@
         <v>0.0003196828991246755</v>
       </c>
       <c r="R13" t="n">
-        <v>0.00143857304606104</v>
+        <v>0.00287714609212208</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_new30.xlsx
+++ b/eval/results/evaluation_metrics_fisher_new30.xlsx
@@ -617,7 +617,7 @@
         <v>0.3384362170279136</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5076543255418704</v>
+        <v>0.4351322790358889</v>
       </c>
     </row>
     <row r="4">
@@ -657,7 +657,7 @@
         <v>0.005769855204427897</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05192869683985107</v>
+        <v>0.02596434841992554</v>
       </c>
       <c r="M4" t="n">
         <v>0.7851851851851852</v>
@@ -675,7 +675,7 @@
         <v>0.04947522530346203</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1484256759103861</v>
+        <v>0.1113192569327896</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +724,7 @@
         <v>0.322683123188597</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7260370271743433</v>
+        <v>0.5808296217394746</v>
       </c>
       <c r="P5" t="n">
         <v>0.7871485943775101</v>
@@ -824,7 +824,7 @@
         <v>0.001212149850067795</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005454674325305077</v>
+        <v>0.003636449550203385</v>
       </c>
       <c r="P7" t="n">
         <v>0.7615062761506276</v>
@@ -833,7 +833,7 @@
         <v>0.02965208763324016</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1334343943495807</v>
+        <v>0.08895626289972049</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="D8" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8291666666666667</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2802938024679246</v>
+        <v>0.06388474037528354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3894321874804655</v>
+        <v>0.1916542211258506</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.9570552147239264</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03131207263621193</v>
+        <v>0.0001358538592277665</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09393621790863578</v>
+        <v>0.001222684733049898</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="N8" t="n">
-        <v>0.598151417232868</v>
+        <v>3.254588206680611e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7648309444386462</v>
+        <v>2.92912938601255e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8366533864541832</v>
+        <v>0.7205542725173211</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4585808094757875</v>
+        <v>0.0003556851287161614</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5159034106602609</v>
+        <v>0.001600583079222727</v>
       </c>
     </row>
     <row r="9">
@@ -1040,7 +1040,7 @@
         <v>0.04662325538338093</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1398697661501428</v>
+        <v>0.1049023246126071</v>
       </c>
       <c r="P11" t="n">
         <v>0.6267281105990783</v>
@@ -1049,7 +1049,7 @@
         <v>0.09307357223718898</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2094155375336752</v>
+        <v>0.1675324300269402</v>
       </c>
     </row>
     <row r="12">
@@ -1107,7 +1107,7 @@
         <v>0.3011314171654854</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5076543255418704</v>
+        <v>0.4351322790358889</v>
       </c>
     </row>
     <row r="13">
@@ -1156,7 +1156,7 @@
         <v>4.88734866985438e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0004398613802868943</v>
+        <v>0.0002199306901434471</v>
       </c>
       <c r="P13" t="n">
         <v>0.7824427480916031</v>
@@ -1165,7 +1165,7 @@
         <v>0.0003196828991246755</v>
       </c>
       <c r="R13" t="n">
-        <v>0.00287714609212208</v>
+        <v>0.001600583079222727</v>
       </c>
     </row>
   </sheetData>
